--- a/data/fo_dataset.xlsx
+++ b/data/fo_dataset.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Falcon\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Falcon\files\PolarityIQ_RAG_Pipeline\polarityiq_rag\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12585"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12585" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="FO_Intelligence_Dataset" sheetId="1" r:id="rId1"/>
@@ -9336,20 +9336,6 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -9369,6 +9355,20 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -9701,35 +9701,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21"/>
-      <c r="S1" s="21"/>
-      <c r="T1" s="21"/>
-      <c r="U1" s="21"/>
-      <c r="V1" s="21"/>
-      <c r="W1" s="21"/>
-      <c r="X1" s="21"/>
-      <c r="Y1" s="21"/>
-      <c r="Z1" s="21"/>
-      <c r="AA1" s="21"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
+      <c r="Y1" s="28"/>
+      <c r="Z1" s="28"/>
+      <c r="AA1" s="28"/>
     </row>
     <row r="2" spans="1:27" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -9774,7 +9774,7 @@
       <c r="N2" s="1" t="s">
         <v>2875</v>
       </c>
-      <c r="O2" s="31" t="s">
+      <c r="O2" s="25" t="s">
         <v>2866</v>
       </c>
       <c r="P2" s="1" t="s">
@@ -9857,7 +9857,7 @@
       <c r="N3" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O3" s="27"/>
+      <c r="O3" s="21"/>
       <c r="P3" s="4" t="s">
         <v>23</v>
       </c>
@@ -9938,7 +9938,7 @@
       <c r="N4" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="O4" s="28" t="s">
+      <c r="O4" s="22" t="s">
         <v>2878</v>
       </c>
       <c r="P4" s="7" t="s">
@@ -10021,7 +10021,7 @@
       <c r="N5" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O5" s="26" t="s">
+      <c r="O5" s="20" t="s">
         <v>2879</v>
       </c>
       <c r="P5" s="7" t="s">
@@ -10104,7 +10104,7 @@
       <c r="N6" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="O6" s="27" t="s">
+      <c r="O6" s="21" t="s">
         <v>2880</v>
       </c>
       <c r="P6" s="4" t="s">
@@ -10187,7 +10187,7 @@
       <c r="N7" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O7" s="26" t="s">
+      <c r="O7" s="20" t="s">
         <v>2881</v>
       </c>
       <c r="P7" s="7" t="s">
@@ -10270,7 +10270,7 @@
       <c r="N8" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="O8" s="27" t="s">
+      <c r="O8" s="21" t="s">
         <v>2882</v>
       </c>
       <c r="P8" s="4" t="s">
@@ -10353,7 +10353,7 @@
       <c r="N9" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O9" s="26" t="s">
+      <c r="O9" s="20" t="s">
         <v>2883</v>
       </c>
       <c r="P9" s="7" t="s">
@@ -10436,7 +10436,7 @@
       <c r="N10" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="O10" s="26" t="s">
+      <c r="O10" s="20" t="s">
         <v>2884</v>
       </c>
       <c r="P10" s="4" t="s">
@@ -10519,7 +10519,7 @@
       <c r="N11" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="O11" s="28" t="s">
+      <c r="O11" s="22" t="s">
         <v>2885</v>
       </c>
       <c r="P11" s="7" t="s">
@@ -10602,7 +10602,7 @@
       <c r="N12" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O12" s="26" t="s">
+      <c r="O12" s="20" t="s">
         <v>2886</v>
       </c>
       <c r="P12" s="4" t="s">
@@ -10685,7 +10685,7 @@
       <c r="N13" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O13" s="29" t="s">
+      <c r="O13" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P13" s="7" t="s">
@@ -10768,7 +10768,7 @@
       <c r="N14" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O14" s="26" t="s">
+      <c r="O14" s="20" t="s">
         <v>2887</v>
       </c>
       <c r="P14" s="4" t="s">
@@ -10851,7 +10851,7 @@
       <c r="N15" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="O15" s="28" t="s">
+      <c r="O15" s="22" t="s">
         <v>2888</v>
       </c>
       <c r="P15" s="7" t="s">
@@ -10934,7 +10934,7 @@
       <c r="N16" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="O16" s="27" t="s">
+      <c r="O16" s="21" t="s">
         <v>2889</v>
       </c>
       <c r="P16" s="4" t="s">
@@ -11017,7 +11017,7 @@
       <c r="N17" s="19" t="s">
         <v>219</v>
       </c>
-      <c r="O17" s="26" t="s">
+      <c r="O17" s="20" t="s">
         <v>2890</v>
       </c>
       <c r="P17" s="7" t="s">
@@ -11100,7 +11100,7 @@
       <c r="N18" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O18" s="26" t="s">
+      <c r="O18" s="20" t="s">
         <v>2891</v>
       </c>
       <c r="P18" s="4" t="s">
@@ -11183,7 +11183,7 @@
       <c r="N19" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="O19" s="29" t="s">
+      <c r="O19" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P19" s="7" t="s">
@@ -11266,7 +11266,7 @@
       <c r="N20" s="16" t="s">
         <v>255</v>
       </c>
-      <c r="O20" s="27" t="s">
+      <c r="O20" s="21" t="s">
         <v>2892</v>
       </c>
       <c r="P20" s="4" t="s">
@@ -11349,7 +11349,7 @@
       <c r="N21" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O21" s="26" t="s">
+      <c r="O21" s="20" t="s">
         <v>2893</v>
       </c>
       <c r="P21" s="7" t="s">
@@ -11432,7 +11432,7 @@
       <c r="N22" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="O22" s="27" t="s">
+      <c r="O22" s="21" t="s">
         <v>2894</v>
       </c>
       <c r="P22" s="4" t="s">
@@ -11515,7 +11515,7 @@
       <c r="N23" s="17" t="s">
         <v>291</v>
       </c>
-      <c r="O23" s="28" t="s">
+      <c r="O23" s="22" t="s">
         <v>2895</v>
       </c>
       <c r="P23" s="7" t="s">
@@ -11598,7 +11598,7 @@
       <c r="N24" s="16" t="s">
         <v>302</v>
       </c>
-      <c r="O24" s="27" t="s">
+      <c r="O24" s="21" t="s">
         <v>2896</v>
       </c>
       <c r="P24" s="4" t="s">
@@ -11681,7 +11681,7 @@
       <c r="N25" s="17" t="s">
         <v>313</v>
       </c>
-      <c r="O25" s="28" t="s">
+      <c r="O25" s="22" t="s">
         <v>2897</v>
       </c>
       <c r="P25" s="7" t="s">
@@ -11764,7 +11764,7 @@
       <c r="N26" s="16" t="s">
         <v>323</v>
       </c>
-      <c r="O26" s="27" t="s">
+      <c r="O26" s="21" t="s">
         <v>2898</v>
       </c>
       <c r="P26" s="4" t="s">
@@ -11847,7 +11847,7 @@
       <c r="N27" s="17" t="s">
         <v>331</v>
       </c>
-      <c r="O27" s="28" t="s">
+      <c r="O27" s="22" t="s">
         <v>2899</v>
       </c>
       <c r="P27" s="7" t="s">
@@ -11930,7 +11930,7 @@
       <c r="N28" s="16" t="s">
         <v>340</v>
       </c>
-      <c r="O28" s="27" t="s">
+      <c r="O28" s="21" t="s">
         <v>2900</v>
       </c>
       <c r="P28" s="4" t="s">
@@ -12013,7 +12013,7 @@
       <c r="N29" s="17" t="s">
         <v>349</v>
       </c>
-      <c r="O29" s="28" t="s">
+      <c r="O29" s="22" t="s">
         <v>2901</v>
       </c>
       <c r="P29" s="7" t="s">
@@ -12096,7 +12096,7 @@
       <c r="N30" s="16" t="s">
         <v>360</v>
       </c>
-      <c r="O30" s="27" t="s">
+      <c r="O30" s="21" t="s">
         <v>2902</v>
       </c>
       <c r="P30" s="4" t="s">
@@ -12179,7 +12179,7 @@
       <c r="N31" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O31" s="26" t="s">
+      <c r="O31" s="20" t="s">
         <v>2903</v>
       </c>
       <c r="P31" s="7" t="s">
@@ -12262,7 +12262,7 @@
       <c r="N32" s="16" t="s">
         <v>386</v>
       </c>
-      <c r="O32" s="27" t="s">
+      <c r="O32" s="21" t="s">
         <v>2904</v>
       </c>
       <c r="P32" s="4" t="s">
@@ -12345,7 +12345,7 @@
       <c r="N33" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O33" s="29" t="s">
+      <c r="O33" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P33" s="7" t="s">
@@ -12428,7 +12428,7 @@
       <c r="N34" s="18" t="s">
         <v>244</v>
       </c>
-      <c r="O34" s="26" t="s">
+      <c r="O34" s="20" t="s">
         <v>2905</v>
       </c>
       <c r="P34" s="4" t="s">
@@ -12511,7 +12511,7 @@
       <c r="N35" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O35" s="29" t="s">
+      <c r="O35" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P35" s="7" t="s">
@@ -12594,7 +12594,7 @@
       <c r="N36" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O36" s="30" t="s">
+      <c r="O36" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P36" s="4" t="s">
@@ -12677,7 +12677,7 @@
       <c r="N37" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O37" s="29" t="s">
+      <c r="O37" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P37" s="7" t="s">
@@ -12760,7 +12760,7 @@
       <c r="N38" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O38" s="30" t="s">
+      <c r="O38" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P38" s="4" t="s">
@@ -12843,7 +12843,7 @@
       <c r="N39" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O39" s="29" t="s">
+      <c r="O39" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P39" s="7" t="s">
@@ -12926,7 +12926,7 @@
       <c r="N40" s="16" t="s">
         <v>472</v>
       </c>
-      <c r="O40" s="27" t="s">
+      <c r="O40" s="21" t="s">
         <v>2906</v>
       </c>
       <c r="P40" s="4" t="s">
@@ -13009,7 +13009,7 @@
       <c r="N41" s="17" t="s">
         <v>484</v>
       </c>
-      <c r="O41" s="28" t="s">
+      <c r="O41" s="22" t="s">
         <v>2907</v>
       </c>
       <c r="P41" s="7" t="s">
@@ -13092,7 +13092,7 @@
       <c r="N42" s="16" t="s">
         <v>496</v>
       </c>
-      <c r="O42" s="27" t="s">
+      <c r="O42" s="21" t="s">
         <v>2908</v>
       </c>
       <c r="P42" s="4" t="s">
@@ -13175,7 +13175,7 @@
       <c r="N43" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O43" s="29" t="s">
+      <c r="O43" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P43" s="7" t="s">
@@ -13258,7 +13258,7 @@
       <c r="N44" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O44" s="26" t="s">
+      <c r="O44" s="20" t="s">
         <v>2909</v>
       </c>
       <c r="P44" s="4" t="s">
@@ -13341,7 +13341,7 @@
       <c r="N45" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="O45" s="28" t="s">
+      <c r="O45" s="22" t="s">
         <v>2885</v>
       </c>
       <c r="P45" s="7" t="s">
@@ -13424,7 +13424,7 @@
       <c r="N46" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O46" s="30" t="s">
+      <c r="O46" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P46" s="4" t="s">
@@ -13507,7 +13507,7 @@
       <c r="N47" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O47" s="29" t="s">
+      <c r="O47" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P47" s="7" t="s">
@@ -13590,7 +13590,7 @@
       <c r="N48" s="16" t="s">
         <v>566</v>
       </c>
-      <c r="O48" s="27" t="s">
+      <c r="O48" s="21" t="s">
         <v>2910</v>
       </c>
       <c r="P48" s="4" t="s">
@@ -13673,7 +13673,7 @@
       <c r="N49" s="17" t="s">
         <v>579</v>
       </c>
-      <c r="O49" s="28" t="s">
+      <c r="O49" s="22" t="s">
         <v>2911</v>
       </c>
       <c r="P49" s="7" t="s">
@@ -13756,7 +13756,7 @@
       <c r="N50" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O50" s="30" t="s">
+      <c r="O50" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P50" s="4" t="s">
@@ -13839,7 +13839,7 @@
       <c r="N51" s="17" t="s">
         <v>606</v>
       </c>
-      <c r="O51" s="28" t="s">
+      <c r="O51" s="22" t="s">
         <v>2912</v>
       </c>
       <c r="P51" s="7" t="s">
@@ -13922,7 +13922,7 @@
       <c r="N52" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O52" s="26" t="s">
+      <c r="O52" s="20" t="s">
         <v>2913</v>
       </c>
       <c r="P52" s="4" t="s">
@@ -14005,7 +14005,7 @@
       <c r="N53" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O53" s="29" t="s">
+      <c r="O53" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P53" s="7" t="s">
@@ -14088,7 +14088,7 @@
       <c r="N54" s="16" t="s">
         <v>643</v>
       </c>
-      <c r="O54" s="27" t="s">
+      <c r="O54" s="21" t="s">
         <v>2914</v>
       </c>
       <c r="P54" s="4" t="s">
@@ -14171,7 +14171,7 @@
       <c r="N55" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="O55" s="28" t="s">
+      <c r="O55" s="22" t="s">
         <v>2915</v>
       </c>
       <c r="P55" s="7" t="s">
@@ -14254,7 +14254,7 @@
       <c r="N56" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O56" s="30" t="s">
+      <c r="O56" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P56" s="4" t="s">
@@ -14337,7 +14337,7 @@
       <c r="N57" s="17" t="s">
         <v>678</v>
       </c>
-      <c r="O57" s="28" t="s">
+      <c r="O57" s="22" t="s">
         <v>2916</v>
       </c>
       <c r="P57" s="7" t="s">
@@ -14420,7 +14420,7 @@
       <c r="N58" s="16" t="s">
         <v>690</v>
       </c>
-      <c r="O58" s="27" t="s">
+      <c r="O58" s="21" t="s">
         <v>2917</v>
       </c>
       <c r="P58" s="4" t="s">
@@ -14503,7 +14503,7 @@
       <c r="N59" s="17" t="s">
         <v>701</v>
       </c>
-      <c r="O59" s="28" t="s">
+      <c r="O59" s="22" t="s">
         <v>2918</v>
       </c>
       <c r="P59" s="7" t="s">
@@ -14586,7 +14586,7 @@
       <c r="N60" s="16" t="s">
         <v>712</v>
       </c>
-      <c r="O60" s="27" t="s">
+      <c r="O60" s="21" t="s">
         <v>2919</v>
       </c>
       <c r="P60" s="4" t="s">
@@ -14669,7 +14669,7 @@
       <c r="N61" s="17" t="s">
         <v>722</v>
       </c>
-      <c r="O61" s="28" t="s">
+      <c r="O61" s="22" t="s">
         <v>2920</v>
       </c>
       <c r="P61" s="7" t="s">
@@ -14752,7 +14752,7 @@
       <c r="N62" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O62" s="26" t="s">
+      <c r="O62" s="20" t="s">
         <v>2921</v>
       </c>
       <c r="P62" s="4" t="s">
@@ -14835,7 +14835,7 @@
       <c r="N63" s="17" t="s">
         <v>744</v>
       </c>
-      <c r="O63" s="28" t="s">
+      <c r="O63" s="22" t="s">
         <v>2922</v>
       </c>
       <c r="P63" s="7" t="s">
@@ -14918,7 +14918,7 @@
       <c r="N64" s="16" t="s">
         <v>755</v>
       </c>
-      <c r="O64" s="27" t="s">
+      <c r="O64" s="21" t="s">
         <v>2923</v>
       </c>
       <c r="P64" s="4" t="s">
@@ -15001,7 +15001,7 @@
       <c r="N65" s="17" t="s">
         <v>767</v>
       </c>
-      <c r="O65" s="28" t="s">
+      <c r="O65" s="22" t="s">
         <v>2924</v>
       </c>
       <c r="P65" s="7" t="s">
@@ -15084,7 +15084,7 @@
       <c r="N66" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O66" s="26" t="s">
+      <c r="O66" s="20" t="s">
         <v>2925</v>
       </c>
       <c r="P66" s="4" t="s">
@@ -15167,7 +15167,7 @@
       <c r="N67" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O67" s="29" t="s">
+      <c r="O67" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P67" s="7" t="s">
@@ -15250,7 +15250,7 @@
       <c r="N68" s="16" t="s">
         <v>800</v>
       </c>
-      <c r="O68" s="27" t="s">
+      <c r="O68" s="21" t="s">
         <v>2926</v>
       </c>
       <c r="P68" s="4" t="s">
@@ -15333,7 +15333,7 @@
       <c r="N69" s="19" t="s">
         <v>810</v>
       </c>
-      <c r="O69" s="26" t="s">
+      <c r="O69" s="20" t="s">
         <v>2927</v>
       </c>
       <c r="P69" s="7" t="s">
@@ -15416,7 +15416,7 @@
       <c r="N70" s="16" t="s">
         <v>821</v>
       </c>
-      <c r="O70" s="27" t="s">
+      <c r="O70" s="21" t="s">
         <v>2928</v>
       </c>
       <c r="P70" s="4" t="s">
@@ -15499,7 +15499,7 @@
       <c r="N71" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O71" s="26" t="s">
+      <c r="O71" s="20" t="s">
         <v>2929</v>
       </c>
       <c r="P71" s="7" t="s">
@@ -15582,7 +15582,7 @@
       <c r="N72" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O72" s="26" t="s">
+      <c r="O72" s="20" t="s">
         <v>2930</v>
       </c>
       <c r="P72" s="4" t="s">
@@ -15665,7 +15665,7 @@
       <c r="N73" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O73" s="26" t="s">
+      <c r="O73" s="20" t="s">
         <v>2931</v>
       </c>
       <c r="P73" s="7" t="s">
@@ -15748,7 +15748,7 @@
       <c r="N74" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O74" s="30" t="s">
+      <c r="O74" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P74" s="4" t="s">
@@ -15831,7 +15831,7 @@
       <c r="N75" s="17" t="s">
         <v>879</v>
       </c>
-      <c r="O75" s="28" t="s">
+      <c r="O75" s="22" t="s">
         <v>2932</v>
       </c>
       <c r="P75" s="7" t="s">
@@ -15914,7 +15914,7 @@
       <c r="N76" s="18" t="s">
         <v>891</v>
       </c>
-      <c r="O76" s="26" t="s">
+      <c r="O76" s="20" t="s">
         <v>2933</v>
       </c>
       <c r="P76" s="4" t="s">
@@ -15997,7 +15997,7 @@
       <c r="N77" s="17" t="s">
         <v>902</v>
       </c>
-      <c r="O77" s="28" t="s">
+      <c r="O77" s="22" t="s">
         <v>2934</v>
       </c>
       <c r="P77" s="7" t="s">
@@ -16080,7 +16080,7 @@
       <c r="N78" s="18" t="s">
         <v>916</v>
       </c>
-      <c r="O78" s="30" t="s">
+      <c r="O78" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P78" s="4" t="s">
@@ -16154,7 +16154,7 @@
       <c r="N79" s="17" t="s">
         <v>927</v>
       </c>
-      <c r="O79" s="28" t="s">
+      <c r="O79" s="22" t="s">
         <v>2935</v>
       </c>
       <c r="P79" s="7" t="s">
@@ -16237,7 +16237,7 @@
       <c r="N80" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O80" s="26" t="s">
+      <c r="O80" s="20" t="s">
         <v>2936</v>
       </c>
       <c r="P80" s="4" t="s">
@@ -16320,7 +16320,7 @@
       <c r="N81" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O81" s="26" t="s">
+      <c r="O81" s="20" t="s">
         <v>2937</v>
       </c>
       <c r="P81" s="7" t="s">
@@ -16403,7 +16403,7 @@
       <c r="N82" s="18" t="s">
         <v>244</v>
       </c>
-      <c r="O82" s="26" t="s">
+      <c r="O82" s="20" t="s">
         <v>2938</v>
       </c>
       <c r="P82" s="4" t="s">
@@ -16486,7 +16486,7 @@
       <c r="N83" s="17" t="s">
         <v>972</v>
       </c>
-      <c r="O83" s="28" t="s">
+      <c r="O83" s="22" t="s">
         <v>2939</v>
       </c>
       <c r="P83" s="7" t="s">
@@ -16569,7 +16569,7 @@
       <c r="N84" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O84" s="26" t="s">
+      <c r="O84" s="20" t="s">
         <v>2940</v>
       </c>
       <c r="P84" s="4" t="s">
@@ -16652,7 +16652,7 @@
       <c r="N85" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O85" s="26" t="s">
+      <c r="O85" s="20" t="s">
         <v>2941</v>
       </c>
       <c r="P85" s="7" t="s">
@@ -16735,7 +16735,7 @@
       <c r="N86" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O86" s="26" t="s">
+      <c r="O86" s="20" t="s">
         <v>2942</v>
       </c>
       <c r="P86" s="4" t="s">
@@ -16818,7 +16818,7 @@
       <c r="N87" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O87" s="26" t="s">
+      <c r="O87" s="20" t="s">
         <v>2943</v>
       </c>
       <c r="P87" s="7" t="s">
@@ -16901,7 +16901,7 @@
       <c r="N88" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O88" s="26" t="s">
+      <c r="O88" s="20" t="s">
         <v>2944</v>
       </c>
       <c r="P88" s="4" t="s">
@@ -16984,7 +16984,7 @@
       <c r="N89" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O89" s="32" t="s">
+      <c r="O89" s="26" t="s">
         <v>49</v>
       </c>
       <c r="P89" s="7" t="s">
@@ -17067,7 +17067,7 @@
       <c r="N90" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O90" s="26" t="s">
+      <c r="O90" s="20" t="s">
         <v>2945</v>
       </c>
       <c r="P90" s="4" t="s">
@@ -17150,7 +17150,7 @@
       <c r="N91" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O91" s="26" t="s">
+      <c r="O91" s="20" t="s">
         <v>2946</v>
       </c>
       <c r="P91" s="7" t="s">
@@ -17233,7 +17233,7 @@
       <c r="N92" s="16" t="s">
         <v>1078</v>
       </c>
-      <c r="O92" s="27" t="s">
+      <c r="O92" s="21" t="s">
         <v>49</v>
       </c>
       <c r="P92" s="4" t="s">
@@ -17316,7 +17316,7 @@
       <c r="N93" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O93" s="29" t="s">
+      <c r="O93" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P93" s="7" t="s">
@@ -17399,7 +17399,7 @@
       <c r="N94" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O94" s="30" t="s">
+      <c r="O94" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P94" s="4" t="s">
@@ -17482,7 +17482,7 @@
       <c r="N95" s="17" t="s">
         <v>1112</v>
       </c>
-      <c r="O95" s="28" t="s">
+      <c r="O95" s="22" t="s">
         <v>2947</v>
       </c>
       <c r="P95" s="7" t="s">
@@ -17565,7 +17565,7 @@
       <c r="N96" s="16" t="s">
         <v>1122</v>
       </c>
-      <c r="O96" s="27" t="s">
+      <c r="O96" s="21" t="s">
         <v>2948</v>
       </c>
       <c r="P96" s="4" t="s">
@@ -17648,7 +17648,7 @@
       <c r="N97" s="17" t="s">
         <v>1131</v>
       </c>
-      <c r="O97" s="28" t="s">
+      <c r="O97" s="22" t="s">
         <v>2949</v>
       </c>
       <c r="P97" s="7" t="s">
@@ -17731,7 +17731,7 @@
       <c r="N98" s="16" t="s">
         <v>1143</v>
       </c>
-      <c r="O98" s="27" t="s">
+      <c r="O98" s="21" t="s">
         <v>2950</v>
       </c>
       <c r="P98" s="4" t="s">
@@ -17814,7 +17814,7 @@
       <c r="N99" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O99" s="29" t="s">
+      <c r="O99" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P99" s="7" t="s">
@@ -17897,7 +17897,7 @@
       <c r="N100" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O100" s="26" t="s">
+      <c r="O100" s="20" t="s">
         <v>2951</v>
       </c>
       <c r="P100" s="4" t="s">
@@ -17980,7 +17980,7 @@
       <c r="N101" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O101" s="29" t="s">
+      <c r="O101" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P101" s="7" t="s">
@@ -18063,7 +18063,7 @@
       <c r="N102" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O102" s="30" t="s">
+      <c r="O102" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P102" s="4" t="s">
@@ -18146,7 +18146,7 @@
       <c r="N103" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O103" s="29" t="s">
+      <c r="O103" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P103" s="7" t="s">
@@ -18229,7 +18229,7 @@
       <c r="N104" s="16" t="s">
         <v>1203</v>
       </c>
-      <c r="O104" s="27" t="s">
+      <c r="O104" s="21" t="s">
         <v>2952</v>
       </c>
       <c r="P104" s="4" t="s">
@@ -18312,7 +18312,7 @@
       <c r="N105" s="17" t="s">
         <v>1215</v>
       </c>
-      <c r="O105" s="28" t="s">
+      <c r="O105" s="22" t="s">
         <v>2953</v>
       </c>
       <c r="P105" s="7" t="s">
@@ -18395,7 +18395,7 @@
       <c r="N106" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O106" s="26" t="s">
+      <c r="O106" s="20" t="s">
         <v>2954</v>
       </c>
       <c r="P106" s="4" t="s">
@@ -18478,7 +18478,7 @@
       <c r="N107" s="19" t="s">
         <v>1238</v>
       </c>
-      <c r="O107" s="26" t="s">
+      <c r="O107" s="20" t="s">
         <v>2955</v>
       </c>
       <c r="P107" s="7" t="s">
@@ -18561,7 +18561,7 @@
       <c r="N108" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O108" s="26" t="s">
+      <c r="O108" s="20" t="s">
         <v>2956</v>
       </c>
       <c r="P108" s="4" t="s">
@@ -18644,7 +18644,7 @@
       <c r="N109" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O109" s="29" t="s">
+      <c r="O109" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P109" s="7" t="s">
@@ -18727,7 +18727,7 @@
       <c r="N110" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O110" s="30" t="s">
+      <c r="O110" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P110" s="4" t="s">
@@ -18810,7 +18810,7 @@
       <c r="N111" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O111" s="29" t="s">
+      <c r="O111" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P111" s="7" t="s">
@@ -18893,7 +18893,7 @@
       <c r="N112" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O112" s="30" t="s">
+      <c r="O112" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P112" s="4" t="s">
@@ -18976,7 +18976,7 @@
       <c r="N113" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O113" s="26" t="s">
+      <c r="O113" s="20" t="s">
         <v>2957</v>
       </c>
       <c r="P113" s="7" t="s">
@@ -19059,7 +19059,7 @@
       <c r="N114" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O114" s="26" t="s">
+      <c r="O114" s="20" t="s">
         <v>2958</v>
       </c>
       <c r="P114" s="4" t="s">
@@ -19142,7 +19142,7 @@
       <c r="N115" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O115" s="26" t="s">
+      <c r="O115" s="20" t="s">
         <v>2959</v>
       </c>
       <c r="P115" s="7" t="s">
@@ -19225,7 +19225,7 @@
       <c r="N116" s="18" t="s">
         <v>1238</v>
       </c>
-      <c r="O116" s="30" t="s">
+      <c r="O116" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P116" s="4" t="s">
@@ -19308,7 +19308,7 @@
       <c r="N117" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O117" s="29" t="s">
+      <c r="O117" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P117" s="7" t="s">
@@ -19391,7 +19391,7 @@
       <c r="N118" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O118" s="26" t="s">
+      <c r="O118" s="20" t="s">
         <v>2960</v>
       </c>
       <c r="P118" s="4" t="s">
@@ -19474,7 +19474,7 @@
       <c r="N119" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O119" s="26" t="s">
+      <c r="O119" s="20" t="s">
         <v>2961</v>
       </c>
       <c r="P119" s="7" t="s">
@@ -19557,7 +19557,7 @@
       <c r="N120" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O120" s="26" t="s">
+      <c r="O120" s="20" t="s">
         <v>2962</v>
       </c>
       <c r="P120" s="4" t="s">
@@ -19640,7 +19640,7 @@
       <c r="N121" s="19" t="s">
         <v>1384</v>
       </c>
-      <c r="O121" s="29" t="s">
+      <c r="O121" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P121" s="7" t="s">
@@ -19723,7 +19723,7 @@
       <c r="N122" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O122" s="26" t="s">
+      <c r="O122" s="20" t="s">
         <v>2963</v>
       </c>
       <c r="P122" s="4" t="s">
@@ -19806,7 +19806,7 @@
       <c r="N123" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O123" s="26" t="s">
+      <c r="O123" s="20" t="s">
         <v>2964</v>
       </c>
       <c r="P123" s="7" t="s">
@@ -19889,7 +19889,7 @@
       <c r="N124" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O124" s="30" t="s">
+      <c r="O124" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P124" s="4" t="s">
@@ -19972,7 +19972,7 @@
       <c r="N125" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O125" s="26" t="s">
+      <c r="O125" s="20" t="s">
         <v>2965</v>
       </c>
       <c r="P125" s="7" t="s">
@@ -20055,7 +20055,7 @@
       <c r="N126" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O126" s="26" t="s">
+      <c r="O126" s="20" t="s">
         <v>2966</v>
       </c>
       <c r="P126" s="4" t="s">
@@ -20138,7 +20138,7 @@
       <c r="N127" s="19" t="s">
         <v>1455</v>
       </c>
-      <c r="O127" s="29" t="s">
+      <c r="O127" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P127" s="7" t="s">
@@ -20221,7 +20221,7 @@
       <c r="N128" s="18" t="s">
         <v>1455</v>
       </c>
-      <c r="O128" s="30" t="s">
+      <c r="O128" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P128" s="4" t="s">
@@ -20304,7 +20304,7 @@
       <c r="N129" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O129" s="26" t="s">
+      <c r="O129" s="20" t="s">
         <v>2967</v>
       </c>
       <c r="P129" s="7" t="s">
@@ -20387,7 +20387,7 @@
       <c r="N130" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O130" s="30" t="s">
+      <c r="O130" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P130" s="4" t="s">
@@ -20470,7 +20470,7 @@
       <c r="N131" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O131" s="26" t="s">
+      <c r="O131" s="20" t="s">
         <v>2968</v>
       </c>
       <c r="P131" s="7" t="s">
@@ -20553,7 +20553,7 @@
       <c r="N132" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O132" s="26" t="s">
+      <c r="O132" s="20" t="s">
         <v>2969</v>
       </c>
       <c r="P132" s="4" t="s">
@@ -20636,7 +20636,7 @@
       <c r="N133" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O133" s="29" t="s">
+      <c r="O133" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P133" s="7" t="s">
@@ -20719,7 +20719,7 @@
       <c r="N134" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O134" s="26" t="s">
+      <c r="O134" s="20" t="s">
         <v>2970</v>
       </c>
       <c r="P134" s="4" t="s">
@@ -20802,7 +20802,7 @@
       <c r="N135" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O135" s="26" t="s">
+      <c r="O135" s="20" t="s">
         <v>2971</v>
       </c>
       <c r="P135" s="7" t="s">
@@ -20885,7 +20885,7 @@
       <c r="N136" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O136" s="26" t="s">
+      <c r="O136" s="20" t="s">
         <v>2972</v>
       </c>
       <c r="P136" s="4" t="s">
@@ -20968,7 +20968,7 @@
       <c r="N137" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O137" s="29" t="s">
+      <c r="O137" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P137" s="7" t="s">
@@ -21051,7 +21051,7 @@
       <c r="N138" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O138" s="30" t="s">
+      <c r="O138" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P138" s="4" t="s">
@@ -21134,7 +21134,7 @@
       <c r="N139" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O139" s="26" t="s">
+      <c r="O139" s="20" t="s">
         <v>2973</v>
       </c>
       <c r="P139" s="7" t="s">
@@ -21217,7 +21217,7 @@
       <c r="N140" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O140" s="26" t="s">
+      <c r="O140" s="20" t="s">
         <v>2974</v>
       </c>
       <c r="P140" s="4" t="s">
@@ -21300,7 +21300,7 @@
       <c r="N141" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O141" s="29" t="s">
+      <c r="O141" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P141" s="7" t="s">
@@ -21383,7 +21383,7 @@
       <c r="N142" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O142" s="26" t="s">
+      <c r="O142" s="20" t="s">
         <v>2975</v>
       </c>
       <c r="P142" s="4" t="s">
@@ -21466,7 +21466,7 @@
       <c r="N143" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O143" s="26" t="s">
+      <c r="O143" s="20" t="s">
         <v>2976</v>
       </c>
       <c r="P143" s="7" t="s">
@@ -21549,7 +21549,7 @@
       <c r="N144" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O144" s="26" t="s">
+      <c r="O144" s="20" t="s">
         <v>2977</v>
       </c>
       <c r="P144" s="4" t="s">
@@ -21632,7 +21632,7 @@
       <c r="N145" s="19" t="s">
         <v>1636</v>
       </c>
-      <c r="O145" s="26" t="s">
+      <c r="O145" s="20" t="s">
         <v>2978</v>
       </c>
       <c r="P145" s="7" t="s">
@@ -21715,7 +21715,7 @@
       <c r="N146" s="18" t="s">
         <v>1636</v>
       </c>
-      <c r="O146" s="26" t="s">
+      <c r="O146" s="20" t="s">
         <v>2979</v>
       </c>
       <c r="P146" s="4" t="s">
@@ -21798,7 +21798,7 @@
       <c r="N147" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O147" s="26" t="s">
+      <c r="O147" s="20" t="s">
         <v>2980</v>
       </c>
       <c r="P147" s="7" t="s">
@@ -21881,7 +21881,7 @@
       <c r="N148" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O148" s="26" t="s">
+      <c r="O148" s="20" t="s">
         <v>2981</v>
       </c>
       <c r="P148" s="4" t="s">
@@ -21964,7 +21964,7 @@
       <c r="N149" s="19" t="s">
         <v>810</v>
       </c>
-      <c r="O149" s="26" t="s">
+      <c r="O149" s="20" t="s">
         <v>2982</v>
       </c>
       <c r="P149" s="7" t="s">
@@ -22047,7 +22047,7 @@
       <c r="N150" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O150" s="26" t="s">
+      <c r="O150" s="20" t="s">
         <v>2983</v>
       </c>
       <c r="P150" s="4" t="s">
@@ -22130,7 +22130,7 @@
       <c r="N151" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O151" s="29" t="s">
+      <c r="O151" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P151" s="7" t="s">
@@ -22213,7 +22213,7 @@
       <c r="N152" s="16" t="s">
         <v>1711</v>
       </c>
-      <c r="O152" s="27" t="s">
+      <c r="O152" s="21" t="s">
         <v>2984</v>
       </c>
       <c r="P152" s="4" t="s">
@@ -22296,7 +22296,7 @@
       <c r="N153" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O153" s="26" t="s">
+      <c r="O153" s="20" t="s">
         <v>2985</v>
       </c>
       <c r="P153" s="7" t="s">
@@ -22379,7 +22379,7 @@
       <c r="N154" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O154" s="30" t="s">
+      <c r="O154" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P154" s="4" t="s">
@@ -22462,7 +22462,7 @@
       <c r="N155" s="17" t="s">
         <v>1743</v>
       </c>
-      <c r="O155" s="28" t="s">
+      <c r="O155" s="22" t="s">
         <v>2986</v>
       </c>
       <c r="P155" s="7" t="s">
@@ -22545,7 +22545,7 @@
       <c r="N156" s="16" t="s">
         <v>1753</v>
       </c>
-      <c r="O156" s="27" t="s">
+      <c r="O156" s="21" t="s">
         <v>2987</v>
       </c>
       <c r="P156" s="4" t="s">
@@ -22628,7 +22628,7 @@
       <c r="N157" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O157" s="29" t="s">
+      <c r="O157" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P157" s="7" t="s">
@@ -22711,7 +22711,7 @@
       <c r="N158" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O158" s="30" t="s">
+      <c r="O158" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P158" s="4" t="s">
@@ -22794,7 +22794,7 @@
       <c r="N159" s="17" t="s">
         <v>1787</v>
       </c>
-      <c r="O159" s="28" t="s">
+      <c r="O159" s="22" t="s">
         <v>2988</v>
       </c>
       <c r="P159" s="7" t="s">
@@ -22877,7 +22877,7 @@
       <c r="N160" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O160" s="30" t="s">
+      <c r="O160" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P160" s="4" t="s">
@@ -22960,7 +22960,7 @@
       <c r="N161" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O161" s="26" t="s">
+      <c r="O161" s="20" t="s">
         <v>2989</v>
       </c>
       <c r="P161" s="7" t="s">
@@ -23043,7 +23043,7 @@
       <c r="N162" s="16" t="s">
         <v>1820</v>
       </c>
-      <c r="O162" s="27" t="s">
+      <c r="O162" s="21" t="s">
         <v>2990</v>
       </c>
       <c r="P162" s="4" t="s">
@@ -23126,7 +23126,7 @@
       <c r="N163" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O163" s="29" t="s">
+      <c r="O163" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P163" s="7" t="s">
@@ -23209,7 +23209,7 @@
       <c r="N164" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O164" s="26" t="s">
+      <c r="O164" s="20" t="s">
         <v>2991</v>
       </c>
       <c r="P164" s="4" t="s">
@@ -23292,7 +23292,7 @@
       <c r="N165" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O165" s="29" t="s">
+      <c r="O165" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P165" s="7" t="s">
@@ -23375,7 +23375,7 @@
       <c r="N166" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O166" s="30" t="s">
+      <c r="O166" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P166" s="4" t="s">
@@ -23458,7 +23458,7 @@
       <c r="N167" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O167" s="29" t="s">
+      <c r="O167" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P167" s="7" t="s">
@@ -23532,7 +23532,7 @@
       <c r="N168" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O168" s="26" t="s">
+      <c r="O168" s="20" t="s">
         <v>2992</v>
       </c>
       <c r="P168" s="4" t="s">
@@ -23615,7 +23615,7 @@
       <c r="N169" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="O169" s="26" t="s">
+      <c r="O169" s="20" t="s">
         <v>2993</v>
       </c>
       <c r="P169" s="7" t="s">
@@ -23698,7 +23698,7 @@
       <c r="N170" s="18" t="s">
         <v>244</v>
       </c>
-      <c r="O170" s="26" t="s">
+      <c r="O170" s="20" t="s">
         <v>2994</v>
       </c>
       <c r="P170" s="4" t="s">
@@ -23781,7 +23781,7 @@
       <c r="N171" s="19" t="s">
         <v>891</v>
       </c>
-      <c r="O171" s="26" t="s">
+      <c r="O171" s="20" t="s">
         <v>2995</v>
       </c>
       <c r="P171" s="7" t="s">
@@ -23864,7 +23864,7 @@
       <c r="N172" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O172" s="30" t="s">
+      <c r="O172" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P172" s="4" t="s">
@@ -23947,7 +23947,7 @@
       <c r="N173" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O173" s="26" t="s">
+      <c r="O173" s="20" t="s">
         <v>2996</v>
       </c>
       <c r="P173" s="7" t="s">
@@ -24030,7 +24030,7 @@
       <c r="N174" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O174" s="26" t="s">
+      <c r="O174" s="20" t="s">
         <v>2997</v>
       </c>
       <c r="P174" s="4" t="s">
@@ -24113,7 +24113,7 @@
       <c r="N175" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O175" s="26" t="s">
+      <c r="O175" s="20" t="s">
         <v>2998</v>
       </c>
       <c r="P175" s="7" t="s">
@@ -24196,7 +24196,7 @@
       <c r="N176" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O176" s="30" t="s">
+      <c r="O176" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P176" s="4" t="s">
@@ -24279,7 +24279,7 @@
       <c r="N177" s="17" t="s">
         <v>1968</v>
       </c>
-      <c r="O177" s="28" t="s">
+      <c r="O177" s="22" t="s">
         <v>2999</v>
       </c>
       <c r="P177" s="7" t="s">
@@ -24362,7 +24362,7 @@
       <c r="N178" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O178" s="30" t="s">
+      <c r="O178" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P178" s="4" t="s">
@@ -24445,7 +24445,7 @@
       <c r="N179" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O179" s="26" t="s">
+      <c r="O179" s="20" t="s">
         <v>3000</v>
       </c>
       <c r="P179" s="7" t="s">
@@ -24528,7 +24528,7 @@
       <c r="N180" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O180" s="30" t="s">
+      <c r="O180" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P180" s="4" t="s">
@@ -24611,7 +24611,7 @@
       <c r="N181" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O181" s="29" t="s">
+      <c r="O181" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P181" s="7" t="s">
@@ -24694,7 +24694,7 @@
       <c r="N182" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O182" s="30" t="s">
+      <c r="O182" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P182" s="4" t="s">
@@ -24777,7 +24777,7 @@
       <c r="N183" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O183" s="29" t="s">
+      <c r="O183" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P183" s="7" t="s">
@@ -24860,7 +24860,7 @@
       <c r="N184" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O184" s="26" t="s">
+      <c r="O184" s="20" t="s">
         <v>3001</v>
       </c>
       <c r="P184" s="4" t="s">
@@ -24943,7 +24943,7 @@
       <c r="N185" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O185" s="26" t="s">
+      <c r="O185" s="20" t="s">
         <v>3002</v>
       </c>
       <c r="P185" s="7" t="s">
@@ -25026,7 +25026,7 @@
       <c r="N186" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O186" s="30" t="s">
+      <c r="O186" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P186" s="4" t="s">
@@ -25109,7 +25109,7 @@
       <c r="N187" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O187" s="29" t="s">
+      <c r="O187" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P187" s="7" t="s">
@@ -25192,7 +25192,7 @@
       <c r="N188" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O188" s="30" t="s">
+      <c r="O188" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P188" s="4" t="s">
@@ -25275,7 +25275,7 @@
       <c r="N189" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O189" s="29" t="s">
+      <c r="O189" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P189" s="7" t="s">
@@ -25358,7 +25358,7 @@
       <c r="N190" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O190" s="30" t="s">
+      <c r="O190" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P190" s="4" t="s">
@@ -25441,7 +25441,7 @@
       <c r="N191" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O191" s="26" t="s">
+      <c r="O191" s="20" t="s">
         <v>3003</v>
       </c>
       <c r="P191" s="7" t="s">
@@ -25524,7 +25524,7 @@
       <c r="N192" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O192" s="30" t="s">
+      <c r="O192" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P192" s="4" t="s">
@@ -25607,7 +25607,7 @@
       <c r="N193" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O193" s="29" t="s">
+      <c r="O193" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P193" s="7" t="s">
@@ -25690,7 +25690,7 @@
       <c r="N194" s="16" t="s">
         <v>2144</v>
       </c>
-      <c r="O194" s="27" t="s">
+      <c r="O194" s="21" t="s">
         <v>3004</v>
       </c>
       <c r="P194" s="4" t="s">
@@ -25773,7 +25773,7 @@
       <c r="N195" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O195" s="29" t="s">
+      <c r="O195" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P195" s="7" t="s">
@@ -25856,7 +25856,7 @@
       <c r="N196" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O196" s="30" t="s">
+      <c r="O196" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P196" s="4" t="s">
@@ -25939,7 +25939,7 @@
       <c r="N197" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O197" s="29" t="s">
+      <c r="O197" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P197" s="7" t="s">
@@ -26022,7 +26022,7 @@
       <c r="N198" s="16" t="s">
         <v>2187</v>
       </c>
-      <c r="O198" s="27" t="s">
+      <c r="O198" s="21" t="s">
         <v>3005</v>
       </c>
       <c r="P198" s="4" t="s">
@@ -26105,7 +26105,7 @@
       <c r="N199" s="19" t="s">
         <v>916</v>
       </c>
-      <c r="O199" s="29" t="s">
+      <c r="O199" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P199" s="7" t="s">
@@ -26188,7 +26188,7 @@
       <c r="N200" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O200" s="26" t="s">
+      <c r="O200" s="20" t="s">
         <v>3006</v>
       </c>
       <c r="P200" s="4" t="s">
@@ -26271,7 +26271,7 @@
       <c r="N201" s="19" t="s">
         <v>2220</v>
       </c>
-      <c r="O201" s="26" t="s">
+      <c r="O201" s="20" t="s">
         <v>3007</v>
       </c>
       <c r="P201" s="7" t="s">
@@ -26354,7 +26354,7 @@
       <c r="N202" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O202" s="30" t="s">
+      <c r="O202" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P202" s="4" t="s">
@@ -26437,7 +26437,7 @@
       <c r="N203" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O203" s="29" t="s">
+      <c r="O203" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P203" s="7" t="s">
@@ -26520,7 +26520,7 @@
       <c r="N204" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O204" s="26" t="s">
+      <c r="O204" s="20" t="s">
         <v>3008</v>
       </c>
       <c r="P204" s="4" t="s">
@@ -26603,7 +26603,7 @@
       <c r="N205" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O205" s="29" t="s">
+      <c r="O205" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P205" s="7" t="s">
@@ -26686,7 +26686,7 @@
       <c r="N206" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O206" s="30" t="s">
+      <c r="O206" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P206" s="4" t="s">
@@ -26769,7 +26769,7 @@
       <c r="N207" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O207" s="29" t="s">
+      <c r="O207" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P207" s="7" t="s">
@@ -26852,7 +26852,7 @@
       <c r="N208" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O208" s="26" t="s">
+      <c r="O208" s="20" t="s">
         <v>3009</v>
       </c>
       <c r="P208" s="4" t="s">
@@ -26935,7 +26935,7 @@
       <c r="N209" s="19" t="s">
         <v>810</v>
       </c>
-      <c r="O209" s="26" t="s">
+      <c r="O209" s="20" t="s">
         <v>3010</v>
       </c>
       <c r="P209" s="7" t="s">
@@ -27018,7 +27018,7 @@
       <c r="N210" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O210" s="30" t="s">
+      <c r="O210" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P210" s="4" t="s">
@@ -27101,7 +27101,7 @@
       <c r="N211" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O211" s="26" t="s">
+      <c r="O211" s="20" t="s">
         <v>3011</v>
       </c>
       <c r="P211" s="7" t="s">
@@ -27184,7 +27184,7 @@
       <c r="N212" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O212" s="30" t="s">
+      <c r="O212" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P212" s="4" t="s">
@@ -27267,7 +27267,7 @@
       <c r="N213" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O213" s="26" t="s">
+      <c r="O213" s="20" t="s">
         <v>3012</v>
       </c>
       <c r="P213" s="7" t="s">
@@ -27350,7 +27350,7 @@
       <c r="N214" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O214" s="30" t="s">
+      <c r="O214" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P214" s="4" t="s">
@@ -27433,7 +27433,7 @@
       <c r="N215" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O215" s="26" t="s">
+      <c r="O215" s="20" t="s">
         <v>3013</v>
       </c>
       <c r="P215" s="7" t="s">
@@ -27516,7 +27516,7 @@
       <c r="N216" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O216" s="26" t="s">
+      <c r="O216" s="20" t="s">
         <v>3014</v>
       </c>
       <c r="P216" s="4" t="s">
@@ -27599,7 +27599,7 @@
       <c r="N217" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O217" s="26" t="s">
+      <c r="O217" s="20" t="s">
         <v>3015</v>
       </c>
       <c r="P217" s="7" t="s">
@@ -27682,7 +27682,7 @@
       <c r="N218" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O218" s="26" t="s">
+      <c r="O218" s="20" t="s">
         <v>3016</v>
       </c>
       <c r="P218" s="4" t="s">
@@ -27765,7 +27765,7 @@
       <c r="N219" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O219" s="29" t="s">
+      <c r="O219" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P219" s="7" t="s">
@@ -27848,7 +27848,7 @@
       <c r="N220" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O220" s="30" t="s">
+      <c r="O220" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P220" s="4" t="s">
@@ -27931,7 +27931,7 @@
       <c r="N221" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O221" s="26" t="s">
+      <c r="O221" s="20" t="s">
         <v>3017</v>
       </c>
       <c r="P221" s="7" t="s">
@@ -28014,7 +28014,7 @@
       <c r="N222" s="18" t="s">
         <v>2435</v>
       </c>
-      <c r="O222" s="30" t="s">
+      <c r="O222" s="24" t="s">
         <v>2435</v>
       </c>
       <c r="P222" s="4" t="s">
@@ -28094,7 +28094,7 @@
       <c r="N223" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="O223" s="26" t="s">
+      <c r="O223" s="20" t="s">
         <v>3018</v>
       </c>
       <c r="P223" s="7" t="s">
@@ -28177,7 +28177,7 @@
       <c r="N224" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O224" s="26" t="s">
+      <c r="O224" s="20" t="s">
         <v>3019</v>
       </c>
       <c r="P224" s="4" t="s">
@@ -28260,7 +28260,7 @@
       <c r="N225" s="17" t="s">
         <v>2464</v>
       </c>
-      <c r="O225" s="28" t="s">
+      <c r="O225" s="22" t="s">
         <v>3020</v>
       </c>
       <c r="P225" s="7" t="s">
@@ -28343,7 +28343,7 @@
       <c r="N226" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O226" s="30" t="s">
+      <c r="O226" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P226" s="4" t="s">
@@ -28426,7 +28426,7 @@
       <c r="N227" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O227" s="29" t="s">
+      <c r="O227" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P227" s="7" t="s">
@@ -28509,7 +28509,7 @@
       <c r="N228" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O228" s="30" t="s">
+      <c r="O228" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P228" s="4" t="s">
@@ -28592,7 +28592,7 @@
       <c r="N229" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O229" s="29" t="s">
+      <c r="O229" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P229" s="7" t="s">
@@ -28675,7 +28675,7 @@
       <c r="N230" s="16" t="s">
         <v>2511</v>
       </c>
-      <c r="O230" s="27" t="s">
+      <c r="O230" s="21" t="s">
         <v>3021</v>
       </c>
       <c r="P230" s="4" t="s">
@@ -28758,7 +28758,7 @@
       <c r="N231" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O231" s="29" t="s">
+      <c r="O231" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P231" s="7" t="s">
@@ -28841,7 +28841,7 @@
       <c r="N232" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O232" s="30" t="s">
+      <c r="O232" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P232" s="4" t="s">
@@ -28924,7 +28924,7 @@
       <c r="N233" s="17" t="s">
         <v>2542</v>
       </c>
-      <c r="O233" s="28" t="s">
+      <c r="O233" s="22" t="s">
         <v>3022</v>
       </c>
       <c r="P233" s="7" t="s">
@@ -29007,7 +29007,7 @@
       <c r="N234" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O234" s="30" t="s">
+      <c r="O234" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P234" s="4" t="s">
@@ -29090,7 +29090,7 @@
       <c r="N235" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O235" s="26" t="s">
+      <c r="O235" s="20" t="s">
         <v>3023</v>
       </c>
       <c r="P235" s="7" t="s">
@@ -29173,7 +29173,7 @@
       <c r="N236" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O236" s="26" t="s">
+      <c r="O236" s="20" t="s">
         <v>3024</v>
       </c>
       <c r="P236" s="4" t="s">
@@ -29253,7 +29253,7 @@
       <c r="N237" s="19" t="s">
         <v>2586</v>
       </c>
-      <c r="O237" s="29" t="s">
+      <c r="O237" s="23" t="s">
         <v>2587</v>
       </c>
       <c r="P237" s="7" t="s">
@@ -29327,7 +29327,7 @@
       <c r="N238" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O238" s="26" t="s">
+      <c r="O238" s="20" t="s">
         <v>3025</v>
       </c>
       <c r="P238" s="4" t="s">
@@ -29410,7 +29410,7 @@
       <c r="N239" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O239" s="29" t="s">
+      <c r="O239" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P239" s="7" t="s">
@@ -29493,7 +29493,7 @@
       <c r="N240" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O240" s="26" t="s">
+      <c r="O240" s="20" t="s">
         <v>3026</v>
       </c>
       <c r="P240" s="4" t="s">
@@ -29576,7 +29576,7 @@
       <c r="N241" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O241" s="26" t="s">
+      <c r="O241" s="20" t="s">
         <v>3027</v>
       </c>
       <c r="P241" s="7" t="s">
@@ -29659,7 +29659,7 @@
       <c r="N242" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O242" s="26" t="s">
+      <c r="O242" s="20" t="s">
         <v>3028</v>
       </c>
       <c r="P242" s="4" t="s">
@@ -29742,7 +29742,7 @@
       <c r="N243" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O243" s="29" t="s">
+      <c r="O243" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P243" s="7" t="s">
@@ -29825,7 +29825,7 @@
       <c r="N244" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O244" s="30" t="s">
+      <c r="O244" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P244" s="4" t="s">
@@ -29908,7 +29908,7 @@
       <c r="N245" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O245" s="29" t="s">
+      <c r="O245" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P245" s="7" t="s">
@@ -29991,7 +29991,7 @@
       <c r="N246" s="18" t="s">
         <v>810</v>
       </c>
-      <c r="O246" s="26" t="s">
+      <c r="O246" s="20" t="s">
         <v>3029</v>
       </c>
       <c r="P246" s="4" t="s">
@@ -30074,7 +30074,7 @@
       <c r="N247" s="17" t="s">
         <v>2689</v>
       </c>
-      <c r="O247" s="28" t="s">
+      <c r="O247" s="22" t="s">
         <v>3030</v>
       </c>
       <c r="P247" s="7" t="s">
@@ -30157,7 +30157,7 @@
       <c r="N248" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O248" s="30" t="s">
+      <c r="O248" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P248" s="4" t="s">
@@ -30240,7 +30240,7 @@
       <c r="N249" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="O249" s="29" t="s">
+      <c r="O249" s="23" t="s">
         <v>49</v>
       </c>
       <c r="P249" s="7" t="s">
@@ -30323,7 +30323,7 @@
       <c r="N250" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="O250" s="30" t="s">
+      <c r="O250" s="24" t="s">
         <v>49</v>
       </c>
       <c r="P250" s="4" t="s">
@@ -30406,7 +30406,7 @@
       <c r="N251" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="O251" s="28" t="s">
+      <c r="O251" s="22" t="s">
         <v>3031</v>
       </c>
       <c r="P251" s="7" t="s">
@@ -30627,14 +30627,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="29" t="s">
         <v>2732</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
@@ -30933,10 +30933,10 @@
       <c r="B24" s="12" t="s">
         <v>2734</v>
       </c>
-      <c r="E24" s="23" t="s">
+      <c r="E24" s="31" t="s">
         <v>2765</v>
       </c>
-      <c r="F24" s="24"/>
+      <c r="F24" s="32"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
@@ -30945,10 +30945,10 @@
       <c r="B25" s="9">
         <v>32</v>
       </c>
-      <c r="E25" s="22" t="s">
+      <c r="E25" s="30" t="s">
         <v>2766</v>
       </c>
-      <c r="F25" s="21"/>
+      <c r="F25" s="28"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
@@ -30957,10 +30957,10 @@
       <c r="B26" s="9">
         <v>68</v>
       </c>
-      <c r="E26" s="22" t="s">
+      <c r="E26" s="30" t="s">
         <v>2767</v>
       </c>
-      <c r="F26" s="21"/>
+      <c r="F26" s="28"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
@@ -30969,10 +30969,10 @@
       <c r="B27" s="9">
         <v>79</v>
       </c>
-      <c r="E27" s="22" t="s">
+      <c r="E27" s="30" t="s">
         <v>2768</v>
       </c>
-      <c r="F27" s="21"/>
+      <c r="F27" s="28"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
@@ -30981,10 +30981,10 @@
       <c r="B28" s="9">
         <v>71</v>
       </c>
-      <c r="E28" s="22" t="s">
+      <c r="E28" s="30" t="s">
         <v>2769</v>
       </c>
-      <c r="F28" s="21"/>
+      <c r="F28" s="28"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
@@ -30993,10 +30993,10 @@
       <c r="B29" s="9">
         <v>0</v>
       </c>
-      <c r="E29" s="22" t="s">
+      <c r="E29" s="30" t="s">
         <v>2771</v>
       </c>
-      <c r="F29" s="21"/>
+      <c r="F29" s="28"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
@@ -31005,49 +31005,49 @@
       <c r="B30" s="10">
         <v>250</v>
       </c>
-      <c r="E30" s="22" t="s">
+      <c r="E30" s="30" t="s">
         <v>2772</v>
       </c>
-      <c r="F30" s="21"/>
+      <c r="F30" s="28"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E31" s="22" t="s">
+      <c r="E31" s="30" t="s">
         <v>2773</v>
       </c>
-      <c r="F31" s="21"/>
+      <c r="F31" s="28"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E32" s="22" t="s">
+      <c r="E32" s="30" t="s">
         <v>2774</v>
       </c>
-      <c r="F32" s="21"/>
+      <c r="F32" s="28"/>
     </row>
     <row r="33" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E33" s="22" t="s">
+      <c r="E33" s="30" t="s">
         <v>2775</v>
       </c>
-      <c r="F33" s="21"/>
+      <c r="F33" s="28"/>
     </row>
     <row r="34" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E34" s="22" t="s">
+      <c r="E34" s="30" t="s">
         <v>2776</v>
       </c>
-      <c r="F34" s="21"/>
+      <c r="F34" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="E32:F32"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E33:F33"/>
     <mergeCell ref="E27:F27"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="E31:F31"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="E32:F32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
